--- a/artfynd/A 26649-2024 artfynd.xlsx
+++ b/artfynd/A 26649-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY46"/>
+  <dimension ref="A1:AY48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5337,6 +5337,210 @@
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>123319478</v>
+      </c>
+      <c r="B47" t="n">
+        <v>82553</v>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>1312</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Gammelgransskål</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Pseudographis pinicola</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>(Nyl.) Rehm</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>storbäcken, Hjd</t>
+        </is>
+      </c>
+      <c r="Q47" t="n">
+        <v>403490</v>
+      </c>
+      <c r="R47" t="n">
+        <v>6961755</v>
+      </c>
+      <c r="S47" t="n">
+        <v>25</v>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>2024-10-30</t>
+        </is>
+      </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>2024-10-30</t>
+        </is>
+      </c>
+      <c r="AD47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT47" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>Håkan Blomqvist</t>
+        </is>
+      </c>
+      <c r="AX47" t="inlineStr">
+        <is>
+          <t>Håkan Blomqvist</t>
+        </is>
+      </c>
+      <c r="AY47" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>123319479</v>
+      </c>
+      <c r="B48" t="n">
+        <v>82553</v>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>1312</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Gammelgransskål</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Pseudographis pinicola</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>(Nyl.) Rehm</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>storbäcken, Hjd</t>
+        </is>
+      </c>
+      <c r="Q48" t="n">
+        <v>403507</v>
+      </c>
+      <c r="R48" t="n">
+        <v>6961738</v>
+      </c>
+      <c r="S48" t="n">
+        <v>25</v>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y48" t="inlineStr">
+        <is>
+          <t>2024-10-30</t>
+        </is>
+      </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>2024-10-30</t>
+        </is>
+      </c>
+      <c r="AD48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT48" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>Håkan Blomqvist</t>
+        </is>
+      </c>
+      <c r="AX48" t="inlineStr">
+        <is>
+          <t>Håkan Blomqvist</t>
+        </is>
+      </c>
+      <c r="AY48" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 26649-2024 artfynd.xlsx
+++ b/artfynd/A 26649-2024 artfynd.xlsx
@@ -5342,7 +5342,7 @@
         <v>123319478</v>
       </c>
       <c r="B47" t="n">
-        <v>82553</v>
+        <v>82556</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5444,7 +5444,7 @@
         <v>123319479</v>
       </c>
       <c r="B48" t="n">
-        <v>82553</v>
+        <v>82556</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>

--- a/artfynd/A 26649-2024 artfynd.xlsx
+++ b/artfynd/A 26649-2024 artfynd.xlsx
@@ -5339,10 +5339,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>123319478</v>
+        <v>123319479</v>
       </c>
       <c r="B47" t="n">
-        <v>82556</v>
+        <v>82558</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5379,10 +5379,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>403490</v>
+        <v>403507</v>
       </c>
       <c r="R47" t="n">
-        <v>6961755</v>
+        <v>6961738</v>
       </c>
       <c r="S47" t="n">
         <v>25</v>
@@ -5441,10 +5441,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>123319479</v>
+        <v>123319478</v>
       </c>
       <c r="B48" t="n">
-        <v>82556</v>
+        <v>82558</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5481,10 +5481,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>403507</v>
+        <v>403490</v>
       </c>
       <c r="R48" t="n">
-        <v>6961738</v>
+        <v>6961755</v>
       </c>
       <c r="S48" t="n">
         <v>25</v>

--- a/artfynd/A 26649-2024 artfynd.xlsx
+++ b/artfynd/A 26649-2024 artfynd.xlsx
@@ -5339,10 +5339,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>123319479</v>
+        <v>123319478</v>
       </c>
       <c r="B47" t="n">
-        <v>82558</v>
+        <v>82559</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5379,10 +5379,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>403507</v>
+        <v>403490</v>
       </c>
       <c r="R47" t="n">
-        <v>6961738</v>
+        <v>6961755</v>
       </c>
       <c r="S47" t="n">
         <v>25</v>
@@ -5441,10 +5441,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>123319478</v>
+        <v>123319479</v>
       </c>
       <c r="B48" t="n">
-        <v>82558</v>
+        <v>82559</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5481,10 +5481,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>403490</v>
+        <v>403507</v>
       </c>
       <c r="R48" t="n">
-        <v>6961755</v>
+        <v>6961738</v>
       </c>
       <c r="S48" t="n">
         <v>25</v>

--- a/artfynd/A 26649-2024 artfynd.xlsx
+++ b/artfynd/A 26649-2024 artfynd.xlsx
@@ -5342,7 +5342,7 @@
         <v>123319478</v>
       </c>
       <c r="B47" t="n">
-        <v>82559</v>
+        <v>82562</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5444,7 +5444,7 @@
         <v>123319479</v>
       </c>
       <c r="B48" t="n">
-        <v>82559</v>
+        <v>82562</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>

--- a/artfynd/A 26649-2024 artfynd.xlsx
+++ b/artfynd/A 26649-2024 artfynd.xlsx
@@ -5339,10 +5339,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>123319478</v>
+        <v>123319479</v>
       </c>
       <c r="B47" t="n">
-        <v>82562</v>
+        <v>82568</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5379,10 +5379,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>403490</v>
+        <v>403507</v>
       </c>
       <c r="R47" t="n">
-        <v>6961755</v>
+        <v>6961738</v>
       </c>
       <c r="S47" t="n">
         <v>25</v>
@@ -5441,10 +5441,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>123319479</v>
+        <v>123319478</v>
       </c>
       <c r="B48" t="n">
-        <v>82562</v>
+        <v>82568</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5481,10 +5481,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>403507</v>
+        <v>403490</v>
       </c>
       <c r="R48" t="n">
-        <v>6961738</v>
+        <v>6961755</v>
       </c>
       <c r="S48" t="n">
         <v>25</v>

--- a/artfynd/A 26649-2024 artfynd.xlsx
+++ b/artfynd/A 26649-2024 artfynd.xlsx
@@ -5339,10 +5339,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>123319479</v>
+        <v>123319478</v>
       </c>
       <c r="B47" t="n">
-        <v>82568</v>
+        <v>82573</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5379,10 +5379,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>403507</v>
+        <v>403490</v>
       </c>
       <c r="R47" t="n">
-        <v>6961738</v>
+        <v>6961755</v>
       </c>
       <c r="S47" t="n">
         <v>25</v>
@@ -5441,10 +5441,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>123319478</v>
+        <v>123319479</v>
       </c>
       <c r="B48" t="n">
-        <v>82568</v>
+        <v>82573</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5481,10 +5481,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>403490</v>
+        <v>403507</v>
       </c>
       <c r="R48" t="n">
-        <v>6961755</v>
+        <v>6961738</v>
       </c>
       <c r="S48" t="n">
         <v>25</v>

--- a/artfynd/A 26649-2024 artfynd.xlsx
+++ b/artfynd/A 26649-2024 artfynd.xlsx
@@ -5339,10 +5339,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>123319478</v>
+        <v>123319479</v>
       </c>
       <c r="B47" t="n">
-        <v>82573</v>
+        <v>82575</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5379,10 +5379,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>403490</v>
+        <v>403507</v>
       </c>
       <c r="R47" t="n">
-        <v>6961755</v>
+        <v>6961738</v>
       </c>
       <c r="S47" t="n">
         <v>25</v>
@@ -5441,10 +5441,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>123319479</v>
+        <v>123319478</v>
       </c>
       <c r="B48" t="n">
-        <v>82573</v>
+        <v>82575</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5481,10 +5481,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>403507</v>
+        <v>403490</v>
       </c>
       <c r="R48" t="n">
-        <v>6961738</v>
+        <v>6961755</v>
       </c>
       <c r="S48" t="n">
         <v>25</v>

--- a/artfynd/A 26649-2024 artfynd.xlsx
+++ b/artfynd/A 26649-2024 artfynd.xlsx
@@ -5339,7 +5339,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>123319479</v>
+        <v>123319478</v>
       </c>
       <c r="B47" t="n">
         <v>82575</v>
@@ -5379,10 +5379,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>403507</v>
+        <v>403490</v>
       </c>
       <c r="R47" t="n">
-        <v>6961738</v>
+        <v>6961755</v>
       </c>
       <c r="S47" t="n">
         <v>25</v>
@@ -5441,7 +5441,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>123319478</v>
+        <v>123319479</v>
       </c>
       <c r="B48" t="n">
         <v>82575</v>
@@ -5481,10 +5481,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>403490</v>
+        <v>403507</v>
       </c>
       <c r="R48" t="n">
-        <v>6961755</v>
+        <v>6961738</v>
       </c>
       <c r="S48" t="n">
         <v>25</v>

--- a/artfynd/A 26649-2024 artfynd.xlsx
+++ b/artfynd/A 26649-2024 artfynd.xlsx
@@ -5339,7 +5339,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>123319478</v>
+        <v>123319479</v>
       </c>
       <c r="B47" t="n">
         <v>82575</v>
@@ -5379,10 +5379,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>403490</v>
+        <v>403507</v>
       </c>
       <c r="R47" t="n">
-        <v>6961755</v>
+        <v>6961738</v>
       </c>
       <c r="S47" t="n">
         <v>25</v>
@@ -5441,7 +5441,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>123319479</v>
+        <v>123319478</v>
       </c>
       <c r="B48" t="n">
         <v>82575</v>
@@ -5481,10 +5481,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>403507</v>
+        <v>403490</v>
       </c>
       <c r="R48" t="n">
-        <v>6961738</v>
+        <v>6961755</v>
       </c>
       <c r="S48" t="n">
         <v>25</v>

--- a/artfynd/A 26649-2024 artfynd.xlsx
+++ b/artfynd/A 26649-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY48"/>
+  <dimension ref="A1:AY47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,50 +675,48 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119017583</v>
+        <v>119024125</v>
       </c>
       <c r="B2" t="n">
-        <v>95424</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92123</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Lappticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Amylocystis lapponica</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Romell) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Berg, Hjd</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>403274</v>
+        <v>403303</v>
       </c>
       <c r="R2" t="n">
-        <v>6961465</v>
+        <v>6961691</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -759,6 +757,7 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -780,12 +779,7 @@
         <v>119017561</v>
       </c>
       <c r="B3" t="n">
-        <v>95424</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97358</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -879,15 +873,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119016397</v>
+        <v>119017583</v>
       </c>
       <c r="B4" t="n">
-        <v>79100</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97358</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -895,21 +884,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>229821</v>
+        <v>53</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +908,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>403265</v>
+        <v>403274</v>
       </c>
       <c r="R4" t="n">
-        <v>6961667</v>
+        <v>6961465</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,37 +970,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119015032</v>
+        <v>119018495</v>
       </c>
       <c r="B5" t="n">
-        <v>90549</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92637</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5432</v>
+        <v>67</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Sprickporing</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Diplomitoporus crustulinus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Bres.) Domański</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1005,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>403475</v>
+        <v>403319</v>
       </c>
       <c r="R5" t="n">
-        <v>6961748</v>
+        <v>6961719</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1083,37 +1067,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119017313</v>
+        <v>119015946</v>
       </c>
       <c r="B6" t="n">
-        <v>82290</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83292</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1312</v>
+        <v>306</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Kornig nållav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Chaenotheca chlorella</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1123,10 +1102,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>403361</v>
+        <v>403351</v>
       </c>
       <c r="R6" t="n">
-        <v>6961513</v>
+        <v>6961656</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1185,15 +1164,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119015246</v>
+        <v>119024141</v>
       </c>
       <c r="B7" t="n">
-        <v>82290</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1201,34 +1175,37 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1312</v>
+        <v>1202</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Berg, Hjd</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>403540</v>
+        <v>403319</v>
       </c>
       <c r="R7" t="n">
-        <v>6961736</v>
+        <v>6961719</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1269,6 +1246,7 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1287,56 +1265,48 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119024919</v>
+        <v>119016596</v>
       </c>
       <c r="B8" t="n">
-        <v>90585</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91923</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>3277</v>
+        <v>1204</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Luddfingersvamp</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alloclavaria purpurea</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(O.F.Müll.:Fr.) Dentinger &amp; D.J.McLaughlin</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Storbäcken Storsjö, Storsjö, Hjd</t>
+          <t>Berg, Hjd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>403573</v>
+        <v>403319</v>
       </c>
       <c r="R8" t="n">
-        <v>6961710</v>
+        <v>6961609</v>
       </c>
       <c r="S8" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1374,7 +1344,6 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1393,37 +1362,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119018550</v>
+        <v>119018685</v>
       </c>
       <c r="B9" t="n">
-        <v>79129</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91923</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6453</v>
+        <v>1204</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1433,10 +1397,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>403328</v>
+        <v>403436</v>
       </c>
       <c r="R9" t="n">
-        <v>6961729</v>
+        <v>6961773</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1495,15 +1459,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119024141</v>
+        <v>119015246</v>
       </c>
       <c r="B10" t="n">
-        <v>90531</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1511,37 +1470,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1202</v>
+        <v>1312</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Berg, Hjd</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>403319</v>
+        <v>403540</v>
       </c>
       <c r="R10" t="n">
-        <v>6961719</v>
+        <v>6961736</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1582,7 +1538,6 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1601,15 +1556,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>119017611</v>
+        <v>119017127</v>
       </c>
       <c r="B11" t="n">
-        <v>89602</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1617,21 +1567,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1962</v>
+        <v>1312</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1641,10 +1591,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>403261</v>
+        <v>403394</v>
       </c>
       <c r="R11" t="n">
-        <v>6961451</v>
+        <v>6961566</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1703,15 +1653,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>119016442</v>
+        <v>119017313</v>
       </c>
       <c r="B12" t="n">
-        <v>78511</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1719,21 +1664,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1743,10 +1688,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>403269</v>
+        <v>403361</v>
       </c>
       <c r="R12" t="n">
-        <v>6961656</v>
+        <v>6961513</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1805,37 +1750,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>119017616</v>
+        <v>119017490</v>
       </c>
       <c r="B13" t="n">
-        <v>90496</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5447</v>
+        <v>1312</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1845,10 +1785,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>403261</v>
+        <v>403292</v>
       </c>
       <c r="R13" t="n">
-        <v>6961451</v>
+        <v>6961490</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1907,15 +1847,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>119017485</v>
+        <v>123319478</v>
       </c>
       <c r="B14" t="n">
-        <v>90549</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1923,37 +1858,37 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5432</v>
+        <v>1312</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Berg, Hjd</t>
+          <t>storbäcken, Hjd</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>403292</v>
+        <v>403490</v>
       </c>
       <c r="R14" t="n">
-        <v>6961490</v>
+        <v>6961755</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -1977,12 +1912,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2024-08-09</t>
+          <t>2024-10-30</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2024-08-09</t>
+          <t>2024-10-30</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -1997,66 +1932,57 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Blomqvist</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Blomqvist</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>119024388</v>
+        <v>123319479</v>
       </c>
       <c r="B15" t="n">
-        <v>96831</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>221945</v>
+        <v>1312</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Storbäcken Storsjö, Storsjö, Hjd</t>
+          <t>storbäcken, Hjd</t>
         </is>
       </c>
       <c r="Q15" t="n">
         <v>403507</v>
       </c>
       <c r="R15" t="n">
-        <v>6961648</v>
+        <v>6961738</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2083,12 +2009,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2024-08-09</t>
+          <t>2024-10-30</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2024-08-09</t>
+          <t>2024-10-30</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2097,56 +2023,50 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Blomqvist</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Blomqvist</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>119015113</v>
+        <v>119016593</v>
       </c>
       <c r="B16" t="n">
-        <v>97897</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92083</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>221952</v>
+        <v>1503</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2156,10 +2076,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>403485</v>
+        <v>403319</v>
       </c>
       <c r="R16" t="n">
-        <v>6961755</v>
+        <v>6961609</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2218,15 +2138,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>119018661</v>
+        <v>119017611</v>
       </c>
       <c r="B17" t="n">
-        <v>74623</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>90932</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2234,21 +2149,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6440</v>
+        <v>1962</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2258,10 +2173,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>403458</v>
+        <v>403261</v>
       </c>
       <c r="R17" t="n">
-        <v>6961758</v>
+        <v>6961451</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2320,15 +2235,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>119017080</v>
+        <v>119024919</v>
       </c>
       <c r="B18" t="n">
-        <v>57308</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92037</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2336,42 +2246,40 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>3277</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Luddfingersvamp</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alloclavaria purpurea</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(O.F.Müll.) Dentinger &amp; D.J.McLaughlin</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Berg, Hjd</t>
+          <t>Storbäcken Storsjö, Storsjö, Hjd</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>403424</v>
+        <v>403573</v>
       </c>
       <c r="R18" t="n">
-        <v>6961596</v>
+        <v>6961710</v>
       </c>
       <c r="S18" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2409,6 +2317,7 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2427,15 +2336,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>119015364</v>
+        <v>119017234</v>
       </c>
       <c r="B19" t="n">
-        <v>97897</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2443,21 +2347,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>221952</v>
+        <v>5447</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2467,10 +2371,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>403561</v>
+        <v>403366</v>
       </c>
       <c r="R19" t="n">
-        <v>6961727</v>
+        <v>6961538</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2529,37 +2433,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>119016596</v>
+        <v>119017616</v>
       </c>
       <c r="B20" t="n">
-        <v>90545</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1204</v>
+        <v>5447</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2569,10 +2468,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>403319</v>
+        <v>403261</v>
       </c>
       <c r="R20" t="n">
-        <v>6961609</v>
+        <v>6961451</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2631,37 +2530,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>119017163</v>
+        <v>119016365</v>
       </c>
       <c r="B21" t="n">
-        <v>74623</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2671,10 +2565,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>403389</v>
+        <v>403275</v>
       </c>
       <c r="R21" t="n">
-        <v>6961557</v>
+        <v>6961697</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2733,19 +2627,14 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>119018576</v>
+        <v>119016442</v>
       </c>
       <c r="B22" t="n">
-        <v>78511</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
@@ -2773,10 +2662,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>403341</v>
+        <v>403269</v>
       </c>
       <c r="R22" t="n">
-        <v>6961739</v>
+        <v>6961656</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2835,37 +2724,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>119018685</v>
+        <v>119017248</v>
       </c>
       <c r="B23" t="n">
-        <v>90545</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1204</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2875,10 +2759,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>403436</v>
+        <v>403356</v>
       </c>
       <c r="R23" t="n">
-        <v>6961773</v>
+        <v>6961527</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2937,37 +2821,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>119015946</v>
+        <v>119018576</v>
       </c>
       <c r="B24" t="n">
-        <v>74609</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>306</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Kornig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Chaenotheca chlorella</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2977,10 +2856,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>403351</v>
+        <v>403341</v>
       </c>
       <c r="R24" t="n">
-        <v>6961656</v>
+        <v>6961739</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3039,15 +2918,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>119015042</v>
+        <v>119015838</v>
       </c>
       <c r="B25" t="n">
-        <v>74623</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78730</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3055,21 +2929,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6440</v>
+        <v>6437</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3079,10 +2953,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>403475</v>
+        <v>403408</v>
       </c>
       <c r="R25" t="n">
-        <v>6961748</v>
+        <v>6961708</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3141,37 +3015,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>119016593</v>
+        <v>119017812</v>
       </c>
       <c r="B26" t="n">
-        <v>90681</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78730</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1503</v>
+        <v>6437</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3181,10 +3050,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>403319</v>
+        <v>403221</v>
       </c>
       <c r="R26" t="n">
-        <v>6961609</v>
+        <v>6961443</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3243,15 +3112,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>119017294</v>
+        <v>119015042</v>
       </c>
       <c r="B27" t="n">
-        <v>74623</v>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83307</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3283,10 +3147,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>403361</v>
+        <v>403475</v>
       </c>
       <c r="R27" t="n">
-        <v>6961513</v>
+        <v>6961748</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3345,15 +3209,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>119017698</v>
+        <v>119015935</v>
       </c>
       <c r="B28" t="n">
-        <v>57308</v>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83307</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3361,39 +3220,34 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100109</v>
+        <v>6440</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>nyligen använt bo</t>
-        </is>
-      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Berg, Hjd</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>403235</v>
+        <v>403351</v>
       </c>
       <c r="R28" t="n">
-        <v>6961455</v>
+        <v>6961656</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3426,11 +3280,6 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2024-08-09</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>Troligt bo tretåig hackspett</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3457,37 +3306,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>119018495</v>
+        <v>119017163</v>
       </c>
       <c r="B29" t="n">
-        <v>91228</v>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83307</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>67</v>
+        <v>6440</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Sprickporing</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Diplomitoporus crustulinus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Bres.) Domański</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3497,10 +3341,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>403319</v>
+        <v>403389</v>
       </c>
       <c r="R29" t="n">
-        <v>6961719</v>
+        <v>6961557</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3559,15 +3403,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>119017127</v>
+        <v>119017294</v>
       </c>
       <c r="B30" t="n">
-        <v>82290</v>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83307</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3575,21 +3414,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1312</v>
+        <v>6440</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3599,10 +3438,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>403394</v>
+        <v>403361</v>
       </c>
       <c r="R30" t="n">
-        <v>6961566</v>
+        <v>6961513</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3661,37 +3500,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>119017171</v>
+        <v>119017488</v>
       </c>
       <c r="B31" t="n">
-        <v>97897</v>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83307</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>221952</v>
+        <v>6440</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3701,10 +3535,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>403389</v>
+        <v>403292</v>
       </c>
       <c r="R31" t="n">
-        <v>6961557</v>
+        <v>6961490</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3766,12 +3600,7 @@
         <v>119018317</v>
       </c>
       <c r="B32" t="n">
-        <v>74623</v>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83307</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3865,15 +3694,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>119017812</v>
+        <v>119018661</v>
       </c>
       <c r="B33" t="n">
-        <v>77895</v>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83307</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3881,21 +3705,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6437</v>
+        <v>6440</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3905,10 +3729,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>403221</v>
+        <v>403458</v>
       </c>
       <c r="R33" t="n">
-        <v>6961443</v>
+        <v>6961758</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3967,15 +3791,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>119017665</v>
+        <v>119018764</v>
       </c>
       <c r="B34" t="n">
-        <v>90549</v>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83307</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3983,21 +3802,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>5432</v>
+        <v>6440</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4007,10 +3826,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>403235</v>
+        <v>403433</v>
       </c>
       <c r="R34" t="n">
-        <v>6961455</v>
+        <v>6961796</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4069,15 +3888,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>119017248</v>
+        <v>119018550</v>
       </c>
       <c r="B35" t="n">
-        <v>78511</v>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79946</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4085,21 +3899,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4109,10 +3923,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>403356</v>
+        <v>403328</v>
       </c>
       <c r="R35" t="n">
-        <v>6961527</v>
+        <v>6961729</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4171,15 +3985,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>119018764</v>
+        <v>119016733</v>
       </c>
       <c r="B36" t="n">
-        <v>74623</v>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4187,37 +3996,42 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6440</v>
+        <v>100109</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P36" t="inlineStr">
         <is>
           <t>Berg, Hjd</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>403433</v>
+        <v>403343</v>
       </c>
       <c r="R36" t="n">
-        <v>6961796</v>
+        <v>6961581</v>
       </c>
       <c r="S36" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4273,15 +4087,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>119016733</v>
+        <v>119017080</v>
       </c>
       <c r="B37" t="n">
-        <v>57308</v>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4309,7 +4118,7 @@
       <c r="I37" t="inlineStr"/>
       <c r="M37" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
@@ -4318,10 +4127,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>403343</v>
+        <v>403424</v>
       </c>
       <c r="R37" t="n">
-        <v>6961581</v>
+        <v>6961596</v>
       </c>
       <c r="S37" t="n">
         <v>15</v>
@@ -4380,43 +4189,38 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>119015582</v>
+        <v>119017698</v>
       </c>
       <c r="B38" t="n">
-        <v>56520</v>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="M38" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>nyligen använt bo</t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
@@ -4425,13 +4229,13 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>403481</v>
+        <v>403235</v>
       </c>
       <c r="R38" t="n">
-        <v>6961646</v>
+        <v>6961455</v>
       </c>
       <c r="S38" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4461,6 +4265,11 @@
       <c r="AA38" t="inlineStr">
         <is>
           <t>2024-08-09</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Troligt bo tretåig hackspett</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4487,15 +4296,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>119017490</v>
+        <v>119620790</v>
       </c>
       <c r="B39" t="n">
-        <v>82290</v>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4503,37 +4307,49 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1312</v>
+        <v>100109</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr"/>
+      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Berg, Hjd</t>
+          <t>Storbäcken, Storsjö, Hjd</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>403292</v>
+        <v>403339</v>
       </c>
       <c r="R39" t="n">
-        <v>6961490</v>
+        <v>6961635</v>
       </c>
       <c r="S39" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4557,12 +4373,22 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2024-08-09</t>
+          <t>2024-09-08</t>
+        </is>
+      </c>
+      <c r="Z39" t="inlineStr">
+        <is>
+          <t>10:00</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2024-08-09</t>
+          <t>2024-09-08</t>
+        </is>
+      </c>
+      <c r="AB39" t="inlineStr">
+        <is>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4573,31 +4399,31 @@
       </c>
       <c r="AG39" t="b">
         <v>0</v>
+      </c>
+      <c r="AH39" t="inlineStr">
+        <is>
+          <t>Barrträd</t>
+        </is>
       </c>
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Stefan Dahlsten</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Stefan Dahlsten</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>119024259</v>
+        <v>119015582</v>
       </c>
       <c r="B40" t="n">
-        <v>97897</v>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57141</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4605,38 +4431,39 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>221952</v>
+        <v>100138</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
-      <c r="J40" t="inlineStr"/>
-      <c r="K40" t="inlineStr"/>
-      <c r="L40" t="inlineStr"/>
-      <c r="N40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Storbäcken Storsjö, Storsjö, Hjd</t>
+          <t>Berg, Hjd</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>403532</v>
+        <v>403481</v>
       </c>
       <c r="R40" t="n">
-        <v>6961654</v>
+        <v>6961646</v>
       </c>
       <c r="S40" t="n">
         <v>25</v>
@@ -4677,7 +4504,6 @@
       <c r="AE40" t="b">
         <v>0</v>
       </c>
-      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
       </c>
@@ -4696,53 +4522,52 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>119015838</v>
+        <v>119024388</v>
       </c>
       <c r="B41" t="n">
-        <v>77895</v>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97983</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6437</v>
+        <v>221945</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
+      <c r="J41" t="inlineStr"/>
+      <c r="K41" t="inlineStr"/>
+      <c r="L41" t="inlineStr"/>
+      <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Berg, Hjd</t>
+          <t>Storbäcken Storsjö, Storsjö, Hjd</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>403408</v>
+        <v>403507</v>
       </c>
       <c r="R41" t="n">
-        <v>6961708</v>
+        <v>6961648</v>
       </c>
       <c r="S41" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -4780,6 +4605,7 @@
       <c r="AE41" t="b">
         <v>0</v>
       </c>
+      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
@@ -4798,15 +4624,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>119017234</v>
+        <v>119015113</v>
       </c>
       <c r="B42" t="n">
-        <v>90496</v>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99140</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4814,21 +4635,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>5447</v>
+        <v>221952</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4838,10 +4659,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>403366</v>
+        <v>403485</v>
       </c>
       <c r="R42" t="n">
-        <v>6961538</v>
+        <v>6961755</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4900,53 +4721,45 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>119024125</v>
+        <v>119015364</v>
       </c>
       <c r="B43" t="n">
-        <v>90721</v>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99140</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>48</v>
+        <v>221952</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Lappticka</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Amylocystis lapponica</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Romell) Bondartsev &amp; Singer</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
-      <c r="J43" t="inlineStr"/>
-      <c r="K43" t="inlineStr"/>
-      <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
           <t>Berg, Hjd</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>403303</v>
+        <v>403561</v>
       </c>
       <c r="R43" t="n">
-        <v>6961691</v>
+        <v>6961727</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4987,7 +4800,6 @@
       <c r="AE43" t="b">
         <v>0</v>
       </c>
-      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
       </c>
@@ -5006,37 +4818,32 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>119015935</v>
+        <v>119017171</v>
       </c>
       <c r="B44" t="n">
-        <v>74623</v>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99140</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6440</v>
+        <v>221952</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5046,10 +4853,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>403351</v>
+        <v>403389</v>
       </c>
       <c r="R44" t="n">
-        <v>6961656</v>
+        <v>6961557</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5108,53 +4915,52 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>119017488</v>
+        <v>119024259</v>
       </c>
       <c r="B45" t="n">
-        <v>74623</v>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99140</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6440</v>
+        <v>221952</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
+      <c r="J45" t="inlineStr"/>
+      <c r="K45" t="inlineStr"/>
+      <c r="L45" t="inlineStr"/>
+      <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Berg, Hjd</t>
+          <t>Storbäcken Storsjö, Storsjö, Hjd</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>403292</v>
+        <v>403532</v>
       </c>
       <c r="R45" t="n">
-        <v>6961490</v>
+        <v>6961654</v>
       </c>
       <c r="S45" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5192,6 +4998,7 @@
       <c r="AE45" t="b">
         <v>0</v>
       </c>
+      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
       </c>
@@ -5210,15 +5017,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>119620790</v>
+        <v>119016397</v>
       </c>
       <c r="B46" t="n">
-        <v>57310</v>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79917</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5226,49 +5028,37 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>100109</v>
+        <v>229821</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K46" t="inlineStr"/>
-      <c r="L46" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M46" t="inlineStr"/>
-      <c r="N46" t="inlineStr"/>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Storbäcken, Storsjö, Hjd</t>
+          <t>Berg, Hjd</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>403339</v>
+        <v>403265</v>
       </c>
       <c r="R46" t="n">
-        <v>6961635</v>
+        <v>6961667</v>
       </c>
       <c r="S46" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5292,22 +5082,12 @@
       </c>
       <c r="Y46" t="inlineStr">
         <is>
-          <t>2024-09-08</t>
-        </is>
-      </c>
-      <c r="Z46" t="inlineStr">
-        <is>
-          <t>10:00</t>
+          <t>2024-08-09</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2024-09-08</t>
-        </is>
-      </c>
-      <c r="AB46" t="inlineStr">
-        <is>
-          <t>10:30</t>
+          <t>2024-08-09</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5318,36 +5098,26 @@
       </c>
       <c r="AG46" t="b">
         <v>0</v>
-      </c>
-      <c r="AH46" t="inlineStr">
-        <is>
-          <t>Barrträd</t>
-        </is>
       </c>
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Stefan Dahlsten</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Stefan Dahlsten</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>123319479</v>
+        <v>119018628</v>
       </c>
       <c r="B47" t="n">
-        <v>82575</v>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79350</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5355,37 +5125,37 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>1312</v>
+        <v>260591</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Talltagel</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Bryoria fremontii</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>storbäcken, Hjd</t>
+          <t>Berg, Hjd</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>403507</v>
+        <v>403409</v>
       </c>
       <c r="R47" t="n">
-        <v>6961738</v>
+        <v>6961770</v>
       </c>
       <c r="S47" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5409,12 +5179,12 @@
       </c>
       <c r="Y47" t="inlineStr">
         <is>
-          <t>2024-10-30</t>
+          <t>2024-08-09</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>2024-10-30</t>
+          <t>2024-08-09</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5429,117 +5199,15 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Håkan Blomqvist</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Håkan Blomqvist</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
-    </row>
-    <row r="48">
-      <c r="A48" t="n">
-        <v>123319478</v>
-      </c>
-      <c r="B48" t="n">
-        <v>82575</v>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D48" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E48" t="n">
-        <v>1312</v>
-      </c>
-      <c r="F48" t="inlineStr">
-        <is>
-          <t>Gammelgransskål</t>
-        </is>
-      </c>
-      <c r="G48" t="inlineStr">
-        <is>
-          <t>Pseudographis pinicola</t>
-        </is>
-      </c>
-      <c r="H48" t="inlineStr">
-        <is>
-          <t>(Nyl.) Rehm</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr"/>
-      <c r="P48" t="inlineStr">
-        <is>
-          <t>storbäcken, Hjd</t>
-        </is>
-      </c>
-      <c r="Q48" t="n">
-        <v>403490</v>
-      </c>
-      <c r="R48" t="n">
-        <v>6961755</v>
-      </c>
-      <c r="S48" t="n">
-        <v>25</v>
-      </c>
-      <c r="T48" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U48" t="inlineStr">
-        <is>
-          <t>Berg</t>
-        </is>
-      </c>
-      <c r="V48" t="inlineStr">
-        <is>
-          <t>Härjedalen</t>
-        </is>
-      </c>
-      <c r="W48" t="inlineStr">
-        <is>
-          <t>Storsjö</t>
-        </is>
-      </c>
-      <c r="Y48" t="inlineStr">
-        <is>
-          <t>2024-10-30</t>
-        </is>
-      </c>
-      <c r="AA48" t="inlineStr">
-        <is>
-          <t>2024-10-30</t>
-        </is>
-      </c>
-      <c r="AD48" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE48" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG48" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT48" t="inlineStr"/>
-      <c r="AW48" t="inlineStr">
-        <is>
-          <t>Håkan Blomqvist</t>
-        </is>
-      </c>
-      <c r="AX48" t="inlineStr">
-        <is>
-          <t>Håkan Blomqvist</t>
-        </is>
-      </c>
-      <c r="AY48" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 26649-2024 artfynd.xlsx
+++ b/artfynd/A 26649-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY47"/>
+  <dimension ref="A1:AZ47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -773,6 +778,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119024125</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -870,6 +880,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119017561</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -967,6 +982,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119017583</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1064,6 +1084,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119018495</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1161,6 +1186,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119015946</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1262,6 +1292,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119024141</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1359,6 +1394,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119016596</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1456,6 +1496,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119018685</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1553,6 +1598,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119015246</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1650,6 +1700,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119017127</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1747,6 +1802,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119017313</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1844,6 +1904,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119017490</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1941,6 +2006,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123319478</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2038,6 +2108,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123319479</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2135,6 +2210,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119016593</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2232,6 +2312,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119017611</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2333,6 +2418,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119024919</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2430,6 +2520,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119017234</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2527,6 +2622,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119017616</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2624,6 +2724,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119016365</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2721,6 +2826,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119016442</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2818,6 +2928,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119017248</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -2915,6 +3030,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119018576</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3012,6 +3132,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119015838</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3109,6 +3234,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119017812</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3206,6 +3336,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119015042</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3303,6 +3438,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119015935</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3400,6 +3540,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119017163</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3497,6 +3642,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119017294</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3594,6 +3744,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119017488</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3691,6 +3846,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119018317</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -3788,6 +3948,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119018661</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -3885,6 +4050,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119018764</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -3982,6 +4152,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119018550</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4084,6 +4259,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119016733</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4186,6 +4366,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119017080</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4293,6 +4478,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119017698</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4417,6 +4607,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119620790</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4519,6 +4714,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119015582</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4621,6 +4821,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119024388</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -4718,6 +4923,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119015113</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -4815,6 +5025,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119015364</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -4912,6 +5127,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119017171</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5014,6 +5234,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119024259</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5111,6 +5336,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119016397</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5208,8 +5438,61 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119018628</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>